--- a/artfynd/A 11829-2023 artfynd.xlsx
+++ b/artfynd/A 11829-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11829-2023 artfynd.xlsx
+++ b/artfynd/A 11829-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102636172</v>
+        <v>103997403</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjässforshöjden- Hökbergen, Jmt</t>
+          <t>Mellantjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553182.3671341848</v>
+        <v>553119</v>
       </c>
       <c r="R2" t="n">
-        <v>7017870.540708586</v>
+        <v>7017828</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,24 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
@@ -798,12 +794,7 @@
         <v>102636238</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553074.7322847339</v>
+        <v>553075</v>
       </c>
       <c r="R3" t="n">
-        <v>7017839.060856286</v>
+        <v>7017839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +862,9 @@
           <t>2022-07-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,53 +896,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102636227</v>
+        <v>103995719</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjässforshöjden- Hökbergen, Jmt</t>
+          <t>Mellantjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553144.7836231468</v>
+        <v>553154</v>
       </c>
       <c r="R4" t="n">
-        <v>7017854.168463736</v>
+        <v>7017897</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,22 +961,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,60 +985,59 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102636248</v>
+        <v>102636227</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553181.8878498235</v>
+        <v>553145</v>
       </c>
       <c r="R5" t="n">
-        <v>7017926.786054453</v>
+        <v>7017854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1083,9 @@
           <t>2022-07-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-07-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,50 +1117,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103995719</v>
+        <v>102636172</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Jmt</t>
+          <t>Bjässforshöjden- Hökbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553153.9888321018</v>
+        <v>553182</v>
       </c>
       <c r="R6" t="n">
-        <v>7017897.073335793</v>
+        <v>7017870</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,22 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,42 +1199,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995796</v>
+        <v>102636248</v>
       </c>
       <c r="B7" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,34 +1233,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellantjärnen, Jmt</t>
+          <t>Bjässforshöjden- Hökbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553168.4456369876</v>
+        <v>553182</v>
       </c>
       <c r="R7" t="n">
-        <v>7017867.610389976</v>
+        <v>7017927</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,22 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2022-07-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2022-07-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,42 +1304,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103997403</v>
+        <v>103995796</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553119.0842504509</v>
+        <v>553168</v>
       </c>
       <c r="R8" t="n">
-        <v>7017827.642008578</v>
+        <v>7017867</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 11829-2023 artfynd.xlsx
+++ b/artfynd/A 11829-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997403</t>
         </is>
       </c>
     </row>
@@ -893,6 +903,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636238</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995719</t>
         </is>
       </c>
     </row>
@@ -1114,6 +1134,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636227</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636172</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102636248</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,8 +1475,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>